--- a/error_analysis/error_analysis_common_agree.xlsx
+++ b/error_analysis/error_analysis_common_agree.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evelynwang/Desktop/error analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCACD01F-0162-8649-9B4A-8727D59FA90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4287E7D4-3A6C-8047-BF3E-BDACBE5B29BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5920" yWindow="760" windowWidth="23480" windowHeight="17460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5380" yWindow="760" windowWidth="24020" windowHeight="17040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="error_analysis_50" sheetId="1" r:id="rId1"/>
@@ -697,7 +697,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -713,7 +713,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -723,7 +722,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -761,30 +759,14 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -795,7 +777,6 @@
     <xf numFmtId="0" fontId="1" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
@@ -807,6 +788,27 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1249,17 +1251,17 @@
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="5" width="12.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16.1640625" style="42" customWidth="1"/>
-    <col min="7" max="7" width="16.1640625" style="40" customWidth="1"/>
-    <col min="8" max="8" width="16.1640625" style="42" customWidth="1"/>
-    <col min="9" max="9" width="16.1640625" style="28" customWidth="1"/>
-    <col min="10" max="10" width="16.33203125" style="42" customWidth="1"/>
+    <col min="6" max="6" width="16.1640625" style="40" customWidth="1"/>
+    <col min="7" max="7" width="16.1640625" style="38" customWidth="1"/>
+    <col min="8" max="8" width="16.1640625" style="40" customWidth="1"/>
+    <col min="9" max="9" width="16.1640625" style="26" customWidth="1"/>
+    <col min="10" max="10" width="16.33203125" style="40" customWidth="1"/>
     <col min="11" max="11" width="16.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.1640625" style="42" customWidth="1"/>
+    <col min="12" max="12" width="16.1640625" style="40" customWidth="1"/>
     <col min="13" max="13" width="16.6640625" customWidth="1"/>
-    <col min="14" max="14" width="16.1640625" style="42" customWidth="1"/>
+    <col min="14" max="14" width="16.1640625" style="40" customWidth="1"/>
     <col min="15" max="15" width="19.83203125" customWidth="1"/>
-    <col min="16" max="16" width="16.1640625" style="42" customWidth="1"/>
+    <col min="16" max="16" width="16.1640625" style="40" customWidth="1"/>
     <col min="17" max="17" width="21.83203125" customWidth="1"/>
     <col min="18" max="18" width="14.1640625" customWidth="1"/>
     <col min="19" max="19" width="26.1640625" customWidth="1"/>
@@ -1281,37 +1283,37 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="G1" s="35" t="s">
+      <c r="G1" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="29" t="s">
         <v>108</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="L1" s="32" t="s">
+      <c r="L1" s="30" t="s">
         <v>109</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="N1" s="33" t="s">
+      <c r="N1" s="31" t="s">
         <v>110</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="P1" s="34" t="s">
+      <c r="P1" s="32" t="s">
         <v>111</v>
       </c>
       <c r="Q1" s="5" t="s">
@@ -1335,37 +1337,37 @@
       <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="48">
-        <v>1</v>
-      </c>
-      <c r="G2" s="49">
-        <v>1</v>
-      </c>
-      <c r="H2" s="43">
-        <v>0</v>
-      </c>
-      <c r="I2" s="24">
-        <v>0</v>
-      </c>
-      <c r="J2" s="44">
+      <c r="F2" s="46">
+        <v>1</v>
+      </c>
+      <c r="G2" s="47">
+        <v>1</v>
+      </c>
+      <c r="H2" s="41">
+        <v>0</v>
+      </c>
+      <c r="I2" s="22">
+        <v>0</v>
+      </c>
+      <c r="J2" s="42">
         <v>0</v>
       </c>
       <c r="K2" s="7">
         <v>0</v>
       </c>
-      <c r="L2" s="45">
+      <c r="L2" s="43">
         <v>0</v>
       </c>
       <c r="M2" s="8">
         <v>0</v>
       </c>
-      <c r="N2" s="73">
-        <v>1</v>
-      </c>
-      <c r="O2" s="74">
-        <v>1</v>
-      </c>
-      <c r="P2" s="47">
+      <c r="N2" s="57">
+        <v>1</v>
+      </c>
+      <c r="O2" s="58">
+        <v>1</v>
+      </c>
+      <c r="P2" s="45">
         <v>0</v>
       </c>
       <c r="Q2" s="10">
@@ -1391,37 +1393,37 @@
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="50">
-        <v>1</v>
-      </c>
-      <c r="G3" s="82">
-        <v>1</v>
-      </c>
-      <c r="H3" s="83">
-        <v>1</v>
-      </c>
-      <c r="I3" s="84">
-        <v>1</v>
-      </c>
-      <c r="J3" s="54">
-        <v>1</v>
-      </c>
-      <c r="K3" s="55">
-        <v>1</v>
-      </c>
-      <c r="L3" s="45">
+      <c r="F3" s="48">
+        <v>1</v>
+      </c>
+      <c r="G3" s="64">
+        <v>1</v>
+      </c>
+      <c r="H3" s="65">
+        <v>1</v>
+      </c>
+      <c r="I3" s="66">
+        <v>1</v>
+      </c>
+      <c r="J3" s="52">
+        <v>1</v>
+      </c>
+      <c r="K3" s="92">
+        <v>1</v>
+      </c>
+      <c r="L3" s="43">
         <v>0</v>
       </c>
       <c r="M3" s="8">
         <v>0</v>
       </c>
-      <c r="N3" s="46">
+      <c r="N3" s="44">
         <v>0</v>
       </c>
       <c r="O3" s="9">
         <v>0</v>
       </c>
-      <c r="P3" s="47">
+      <c r="P3" s="45">
         <v>0</v>
       </c>
       <c r="Q3" s="10">
@@ -1447,37 +1449,37 @@
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="41">
-        <v>0</v>
-      </c>
-      <c r="G4" s="36">
-        <v>0</v>
-      </c>
-      <c r="H4" s="85">
-        <v>1</v>
-      </c>
-      <c r="I4" s="86">
-        <v>1</v>
-      </c>
-      <c r="J4" s="56">
-        <v>1</v>
-      </c>
-      <c r="K4" s="57">
-        <v>1</v>
-      </c>
-      <c r="L4" s="45">
+      <c r="F4" s="39">
+        <v>0</v>
+      </c>
+      <c r="G4" s="34">
+        <v>0</v>
+      </c>
+      <c r="H4" s="67">
+        <v>1</v>
+      </c>
+      <c r="I4" s="68">
+        <v>1</v>
+      </c>
+      <c r="J4" s="53">
+        <v>1</v>
+      </c>
+      <c r="K4" s="93">
+        <v>1</v>
+      </c>
+      <c r="L4" s="43">
         <v>0</v>
       </c>
       <c r="M4" s="8">
         <v>0</v>
       </c>
-      <c r="N4" s="46">
+      <c r="N4" s="44">
         <v>0</v>
       </c>
       <c r="O4" s="9">
         <v>0</v>
       </c>
-      <c r="P4" s="47">
+      <c r="P4" s="45">
         <v>0</v>
       </c>
       <c r="Q4" s="10">
@@ -1503,43 +1505,43 @@
       <c r="E5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="41">
-        <v>0</v>
-      </c>
-      <c r="G5" s="37">
-        <v>0</v>
-      </c>
-      <c r="H5" s="43">
-        <v>0</v>
-      </c>
-      <c r="I5" s="25">
-        <v>0</v>
-      </c>
-      <c r="J5" s="58">
-        <v>1</v>
-      </c>
-      <c r="K5" s="59">
-        <v>1</v>
-      </c>
-      <c r="L5" s="64">
-        <v>1</v>
-      </c>
-      <c r="M5" s="65">
-        <v>1</v>
-      </c>
-      <c r="N5" s="46">
-        <v>0</v>
-      </c>
-      <c r="O5" s="14">
-        <v>0</v>
-      </c>
-      <c r="P5" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="15">
-        <v>0</v>
-      </c>
-      <c r="R5" s="16">
+      <c r="F5" s="39">
+        <v>0</v>
+      </c>
+      <c r="G5" s="35">
+        <v>0</v>
+      </c>
+      <c r="H5" s="41">
+        <v>0</v>
+      </c>
+      <c r="I5" s="23">
+        <v>0</v>
+      </c>
+      <c r="J5" s="54">
+        <v>1</v>
+      </c>
+      <c r="K5" s="94">
+        <v>1</v>
+      </c>
+      <c r="L5" s="43">
+        <v>0</v>
+      </c>
+      <c r="M5" s="8">
+        <v>0</v>
+      </c>
+      <c r="N5" s="44">
+        <v>0</v>
+      </c>
+      <c r="O5" s="13">
+        <v>0</v>
+      </c>
+      <c r="P5" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="14">
+        <v>0</v>
+      </c>
+      <c r="R5" s="15">
         <v>4</v>
       </c>
     </row>
@@ -1559,43 +1561,43 @@
       <c r="E6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="41">
-        <v>0</v>
-      </c>
-      <c r="G6" s="37">
-        <v>0</v>
-      </c>
-      <c r="H6" s="43">
-        <v>1</v>
-      </c>
-      <c r="I6" s="25">
-        <v>0</v>
-      </c>
-      <c r="J6" s="44">
+      <c r="F6" s="39">
+        <v>0</v>
+      </c>
+      <c r="G6" s="35">
+        <v>0</v>
+      </c>
+      <c r="H6" s="41">
+        <v>1</v>
+      </c>
+      <c r="I6" s="23">
+        <v>0</v>
+      </c>
+      <c r="J6" s="42">
         <v>0</v>
       </c>
       <c r="K6" s="12">
         <v>0</v>
       </c>
-      <c r="L6" s="45">
-        <v>0</v>
-      </c>
-      <c r="M6" s="13">
-        <v>0</v>
-      </c>
-      <c r="N6" s="73">
-        <v>1</v>
-      </c>
-      <c r="O6" s="75">
-        <v>1</v>
-      </c>
-      <c r="P6" s="47">
+      <c r="L6" s="43">
+        <v>0</v>
+      </c>
+      <c r="M6" s="86">
+        <v>0</v>
+      </c>
+      <c r="N6" s="83">
+        <v>1</v>
+      </c>
+      <c r="O6" s="59">
+        <v>1</v>
+      </c>
+      <c r="P6" s="45">
         <v>0</v>
       </c>
       <c r="Q6" s="10">
         <v>0</v>
       </c>
-      <c r="R6" s="17">
+      <c r="R6" s="16">
         <v>5</v>
       </c>
     </row>
@@ -1615,43 +1617,43 @@
       <c r="E7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="41">
-        <v>0</v>
-      </c>
-      <c r="G7" s="37">
-        <v>1</v>
-      </c>
-      <c r="H7" s="43">
-        <v>0</v>
-      </c>
-      <c r="I7" s="25">
-        <v>0</v>
-      </c>
-      <c r="J7" s="54">
-        <v>1</v>
-      </c>
-      <c r="K7" s="60">
-        <v>1</v>
-      </c>
-      <c r="L7" s="66">
-        <v>1</v>
-      </c>
-      <c r="M7" s="67">
-        <v>1</v>
-      </c>
-      <c r="N7" s="46">
-        <v>0</v>
-      </c>
-      <c r="O7" s="14">
-        <v>0</v>
-      </c>
-      <c r="P7" s="47">
+      <c r="F7" s="39">
+        <v>0</v>
+      </c>
+      <c r="G7" s="35">
+        <v>1</v>
+      </c>
+      <c r="H7" s="41">
+        <v>0</v>
+      </c>
+      <c r="I7" s="23">
+        <v>0</v>
+      </c>
+      <c r="J7" s="52">
+        <v>1</v>
+      </c>
+      <c r="K7" s="56">
+        <v>1</v>
+      </c>
+      <c r="L7" s="88">
+        <v>1</v>
+      </c>
+      <c r="M7" s="89">
+        <v>1</v>
+      </c>
+      <c r="N7" s="44">
+        <v>0</v>
+      </c>
+      <c r="O7" s="13">
+        <v>0</v>
+      </c>
+      <c r="P7" s="45">
         <v>0</v>
       </c>
       <c r="Q7" s="10">
         <v>0</v>
       </c>
-      <c r="R7" s="17">
+      <c r="R7" s="16">
         <v>6</v>
       </c>
     </row>
@@ -1671,43 +1673,43 @@
       <c r="E8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="41">
-        <v>0</v>
-      </c>
-      <c r="G8" s="37">
-        <v>0</v>
-      </c>
-      <c r="H8" s="83">
-        <v>1</v>
-      </c>
-      <c r="I8" s="90">
-        <v>1</v>
-      </c>
-      <c r="J8" s="87">
-        <v>1</v>
-      </c>
-      <c r="K8" s="59">
-        <v>1</v>
-      </c>
-      <c r="L8" s="68">
-        <v>1</v>
-      </c>
-      <c r="M8" s="69">
-        <v>1</v>
-      </c>
-      <c r="N8" s="46">
-        <v>0</v>
-      </c>
-      <c r="O8" s="14">
-        <v>0</v>
-      </c>
-      <c r="P8" s="47">
+      <c r="F8" s="39">
+        <v>0</v>
+      </c>
+      <c r="G8" s="35">
+        <v>0</v>
+      </c>
+      <c r="H8" s="65">
+        <v>1</v>
+      </c>
+      <c r="I8" s="71">
+        <v>1</v>
+      </c>
+      <c r="J8" s="69">
+        <v>1</v>
+      </c>
+      <c r="K8" s="82">
+        <v>1</v>
+      </c>
+      <c r="L8" s="90">
+        <v>1</v>
+      </c>
+      <c r="M8" s="91">
+        <v>1</v>
+      </c>
+      <c r="N8" s="44">
+        <v>0</v>
+      </c>
+      <c r="O8" s="13">
+        <v>0</v>
+      </c>
+      <c r="P8" s="45">
         <v>0</v>
       </c>
       <c r="Q8" s="10">
         <v>0</v>
       </c>
-      <c r="R8" s="17">
+      <c r="R8" s="16">
         <v>7</v>
       </c>
     </row>
@@ -1727,43 +1729,43 @@
       <c r="E9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="41">
-        <v>1</v>
-      </c>
-      <c r="G9" s="37">
-        <v>0</v>
-      </c>
-      <c r="H9" s="99">
-        <v>1</v>
-      </c>
-      <c r="I9" s="93">
-        <v>1</v>
-      </c>
-      <c r="J9" s="44">
+      <c r="F9" s="39">
+        <v>1</v>
+      </c>
+      <c r="G9" s="35">
+        <v>0</v>
+      </c>
+      <c r="H9" s="80">
+        <v>1</v>
+      </c>
+      <c r="I9" s="74">
+        <v>1</v>
+      </c>
+      <c r="J9" s="42">
         <v>0</v>
       </c>
       <c r="K9" s="12">
         <v>0</v>
       </c>
-      <c r="L9" s="45">
-        <v>0</v>
-      </c>
-      <c r="M9" s="13">
-        <v>0</v>
-      </c>
-      <c r="N9" s="73">
-        <v>1</v>
-      </c>
-      <c r="O9" s="75">
-        <v>1</v>
-      </c>
-      <c r="P9" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="15">
-        <v>0</v>
-      </c>
-      <c r="R9" s="17">
+      <c r="L9" s="43">
+        <v>0</v>
+      </c>
+      <c r="M9" s="86">
+        <v>0</v>
+      </c>
+      <c r="N9" s="83">
+        <v>1</v>
+      </c>
+      <c r="O9" s="59">
+        <v>1</v>
+      </c>
+      <c r="P9" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="14">
+        <v>0</v>
+      </c>
+      <c r="R9" s="16">
         <v>8</v>
       </c>
     </row>
@@ -1783,43 +1785,43 @@
       <c r="E10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="41">
-        <v>0</v>
-      </c>
-      <c r="G10" s="37">
-        <v>0</v>
-      </c>
-      <c r="H10" s="98">
-        <v>0</v>
-      </c>
-      <c r="I10" s="92">
-        <v>1</v>
-      </c>
-      <c r="J10" s="88">
-        <v>1</v>
-      </c>
-      <c r="K10" s="60">
-        <v>1</v>
-      </c>
-      <c r="L10" s="45">
-        <v>1</v>
-      </c>
-      <c r="M10" s="13">
-        <v>0</v>
-      </c>
-      <c r="N10" s="46">
-        <v>0</v>
-      </c>
-      <c r="O10" s="14">
-        <v>0</v>
-      </c>
-      <c r="P10" s="47">
+      <c r="F10" s="39">
+        <v>0</v>
+      </c>
+      <c r="G10" s="35">
+        <v>0</v>
+      </c>
+      <c r="H10" s="79">
+        <v>0</v>
+      </c>
+      <c r="I10" s="73">
+        <v>1</v>
+      </c>
+      <c r="J10" s="52">
+        <v>1</v>
+      </c>
+      <c r="K10" s="95">
+        <v>1</v>
+      </c>
+      <c r="L10" s="43">
+        <v>0</v>
+      </c>
+      <c r="M10" s="86">
+        <v>0</v>
+      </c>
+      <c r="N10" s="44">
+        <v>0</v>
+      </c>
+      <c r="O10" s="13">
+        <v>0</v>
+      </c>
+      <c r="P10" s="45">
         <v>0</v>
       </c>
       <c r="Q10" s="10">
         <v>0</v>
       </c>
-      <c r="R10" s="17">
+      <c r="R10" s="16">
         <v>9</v>
       </c>
     </row>
@@ -1839,43 +1841,43 @@
       <c r="E11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="41">
-        <v>0</v>
-      </c>
-      <c r="G11" s="37">
-        <v>1</v>
-      </c>
-      <c r="H11" s="83">
-        <v>1</v>
-      </c>
-      <c r="I11" s="90">
-        <v>1</v>
-      </c>
-      <c r="J11" s="44">
-        <v>1</v>
-      </c>
-      <c r="K11" s="61">
-        <v>1</v>
-      </c>
-      <c r="L11" s="64">
-        <v>1</v>
-      </c>
-      <c r="M11" s="65">
-        <v>1</v>
-      </c>
-      <c r="N11" s="46">
-        <v>0</v>
-      </c>
-      <c r="O11" s="14">
-        <v>0</v>
-      </c>
-      <c r="P11" s="47">
+      <c r="F11" s="39">
+        <v>0</v>
+      </c>
+      <c r="G11" s="35">
+        <v>1</v>
+      </c>
+      <c r="H11" s="65">
+        <v>1</v>
+      </c>
+      <c r="I11" s="71">
+        <v>1</v>
+      </c>
+      <c r="J11" s="53">
+        <v>1</v>
+      </c>
+      <c r="K11" s="96">
+        <v>1</v>
+      </c>
+      <c r="L11" s="97">
+        <v>1</v>
+      </c>
+      <c r="M11" s="98">
+        <v>1</v>
+      </c>
+      <c r="N11" s="44">
+        <v>0</v>
+      </c>
+      <c r="O11" s="13">
+        <v>0</v>
+      </c>
+      <c r="P11" s="45">
         <v>0</v>
       </c>
       <c r="Q11" s="10">
         <v>0</v>
       </c>
-      <c r="R11" s="17">
+      <c r="R11" s="16">
         <v>10</v>
       </c>
     </row>
@@ -1895,43 +1897,43 @@
       <c r="E12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="41">
-        <v>0</v>
-      </c>
-      <c r="G12" s="37">
-        <v>0</v>
-      </c>
-      <c r="H12" s="91">
-        <v>1</v>
-      </c>
-      <c r="I12" s="92">
-        <v>1</v>
-      </c>
-      <c r="J12" s="87">
-        <v>1</v>
-      </c>
-      <c r="K12" s="59">
-        <v>1</v>
-      </c>
-      <c r="L12" s="45">
-        <v>0</v>
-      </c>
-      <c r="M12" s="13">
-        <v>0</v>
-      </c>
-      <c r="N12" s="46">
-        <v>0</v>
-      </c>
-      <c r="O12" s="14">
-        <v>0</v>
-      </c>
-      <c r="P12" s="47">
+      <c r="F12" s="39">
+        <v>0</v>
+      </c>
+      <c r="G12" s="35">
+        <v>0</v>
+      </c>
+      <c r="H12" s="72">
+        <v>1</v>
+      </c>
+      <c r="I12" s="73">
+        <v>1</v>
+      </c>
+      <c r="J12" s="54">
+        <v>1</v>
+      </c>
+      <c r="K12" s="94">
+        <v>1</v>
+      </c>
+      <c r="L12" s="43">
+        <v>0</v>
+      </c>
+      <c r="M12" s="86">
+        <v>0</v>
+      </c>
+      <c r="N12" s="44">
+        <v>0</v>
+      </c>
+      <c r="O12" s="13">
+        <v>0</v>
+      </c>
+      <c r="P12" s="45">
         <v>0</v>
       </c>
       <c r="Q12" s="10">
         <v>0</v>
       </c>
-      <c r="R12" s="17">
+      <c r="R12" s="16">
         <v>11</v>
       </c>
     </row>
@@ -1951,43 +1953,43 @@
       <c r="E13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="41">
-        <v>0</v>
-      </c>
-      <c r="G13" s="37">
-        <v>0</v>
-      </c>
-      <c r="H13" s="91">
-        <v>1</v>
-      </c>
-      <c r="I13" s="92">
-        <v>1</v>
-      </c>
-      <c r="J13" s="44">
+      <c r="F13" s="39">
+        <v>0</v>
+      </c>
+      <c r="G13" s="35">
+        <v>0</v>
+      </c>
+      <c r="H13" s="72">
+        <v>1</v>
+      </c>
+      <c r="I13" s="73">
+        <v>1</v>
+      </c>
+      <c r="J13" s="42">
         <v>0</v>
       </c>
       <c r="K13" s="12">
         <v>1</v>
       </c>
-      <c r="L13" s="45">
-        <v>0</v>
-      </c>
-      <c r="M13" s="13">
-        <v>0</v>
-      </c>
-      <c r="N13" s="73">
-        <v>1</v>
-      </c>
-      <c r="O13" s="75">
-        <v>1</v>
-      </c>
-      <c r="P13" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="15">
-        <v>0</v>
-      </c>
-      <c r="R13" s="17">
+      <c r="L13" s="43">
+        <v>0</v>
+      </c>
+      <c r="M13" s="86">
+        <v>0</v>
+      </c>
+      <c r="N13" s="83">
+        <v>1</v>
+      </c>
+      <c r="O13" s="59">
+        <v>1</v>
+      </c>
+      <c r="P13" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="14">
+        <v>0</v>
+      </c>
+      <c r="R13" s="16">
         <v>12</v>
       </c>
     </row>
@@ -2007,43 +2009,43 @@
       <c r="E14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="41">
-        <v>0</v>
-      </c>
-      <c r="G14" s="37">
-        <v>0</v>
-      </c>
-      <c r="H14" s="91">
-        <v>1</v>
-      </c>
-      <c r="I14" s="92">
-        <v>1</v>
-      </c>
-      <c r="J14" s="44">
+      <c r="F14" s="39">
+        <v>0</v>
+      </c>
+      <c r="G14" s="35">
+        <v>0</v>
+      </c>
+      <c r="H14" s="72">
+        <v>1</v>
+      </c>
+      <c r="I14" s="73">
+        <v>1</v>
+      </c>
+      <c r="J14" s="42">
         <v>0</v>
       </c>
       <c r="K14" s="12">
         <v>0</v>
       </c>
-      <c r="L14" s="45">
-        <v>0</v>
-      </c>
-      <c r="M14" s="13">
-        <v>0</v>
-      </c>
-      <c r="N14" s="46">
-        <v>0</v>
-      </c>
-      <c r="O14" s="14">
-        <v>0</v>
-      </c>
-      <c r="P14" s="47">
+      <c r="L14" s="43">
+        <v>0</v>
+      </c>
+      <c r="M14" s="86">
+        <v>0</v>
+      </c>
+      <c r="N14" s="44">
+        <v>0</v>
+      </c>
+      <c r="O14" s="13">
+        <v>0</v>
+      </c>
+      <c r="P14" s="45">
         <v>0</v>
       </c>
       <c r="Q14" s="10">
         <v>0</v>
       </c>
-      <c r="R14" s="17">
+      <c r="R14" s="16">
         <v>13</v>
       </c>
     </row>
@@ -2063,43 +2065,43 @@
       <c r="E15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="41">
-        <v>0</v>
-      </c>
-      <c r="G15" s="37">
-        <v>0</v>
-      </c>
-      <c r="H15" s="91">
-        <v>1</v>
-      </c>
-      <c r="I15" s="92">
-        <v>1</v>
-      </c>
-      <c r="J15" s="88">
-        <v>1</v>
-      </c>
-      <c r="K15" s="60">
-        <v>1</v>
-      </c>
-      <c r="L15" s="64">
-        <v>1</v>
-      </c>
-      <c r="M15" s="65">
-        <v>1</v>
-      </c>
-      <c r="N15" s="46">
-        <v>0</v>
-      </c>
-      <c r="O15" s="14">
-        <v>0</v>
-      </c>
-      <c r="P15" s="47">
+      <c r="F15" s="39">
+        <v>0</v>
+      </c>
+      <c r="G15" s="35">
+        <v>0</v>
+      </c>
+      <c r="H15" s="72">
+        <v>1</v>
+      </c>
+      <c r="I15" s="73">
+        <v>1</v>
+      </c>
+      <c r="J15" s="70">
+        <v>1</v>
+      </c>
+      <c r="K15" s="56">
+        <v>1</v>
+      </c>
+      <c r="L15" s="43">
+        <v>0</v>
+      </c>
+      <c r="M15" s="86">
+        <v>0</v>
+      </c>
+      <c r="N15" s="44">
+        <v>0</v>
+      </c>
+      <c r="O15" s="13">
+        <v>0</v>
+      </c>
+      <c r="P15" s="45">
         <v>0</v>
       </c>
       <c r="Q15" s="10">
         <v>0</v>
       </c>
-      <c r="R15" s="17">
+      <c r="R15" s="16">
         <v>14</v>
       </c>
     </row>
@@ -2119,43 +2121,43 @@
       <c r="E16" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="41">
-        <v>0</v>
-      </c>
-      <c r="G16" s="37">
-        <v>0</v>
-      </c>
-      <c r="H16" s="98">
-        <v>1</v>
-      </c>
-      <c r="I16" s="92">
-        <v>1</v>
-      </c>
-      <c r="J16" s="87">
-        <v>1</v>
-      </c>
-      <c r="K16" s="59">
-        <v>1</v>
-      </c>
-      <c r="L16" s="45">
-        <v>0</v>
-      </c>
-      <c r="M16" s="13">
-        <v>0</v>
-      </c>
-      <c r="N16" s="46">
-        <v>0</v>
-      </c>
-      <c r="O16" s="14">
-        <v>0</v>
-      </c>
-      <c r="P16" s="47">
+      <c r="F16" s="39">
+        <v>0</v>
+      </c>
+      <c r="G16" s="35">
+        <v>0</v>
+      </c>
+      <c r="H16" s="79">
+        <v>1</v>
+      </c>
+      <c r="I16" s="73">
+        <v>1</v>
+      </c>
+      <c r="J16" s="69">
+        <v>1</v>
+      </c>
+      <c r="K16" s="82">
+        <v>1</v>
+      </c>
+      <c r="L16" s="43">
+        <v>0</v>
+      </c>
+      <c r="M16" s="86">
+        <v>0</v>
+      </c>
+      <c r="N16" s="44">
+        <v>0</v>
+      </c>
+      <c r="O16" s="13">
+        <v>0</v>
+      </c>
+      <c r="P16" s="45">
         <v>0</v>
       </c>
       <c r="Q16" s="10">
         <v>0</v>
       </c>
-      <c r="R16" s="17">
+      <c r="R16" s="16">
         <v>15</v>
       </c>
     </row>
@@ -2175,43 +2177,43 @@
       <c r="E17" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="41">
-        <v>0</v>
-      </c>
-      <c r="G17" s="37">
-        <v>0</v>
-      </c>
-      <c r="H17" s="91">
-        <v>1</v>
-      </c>
-      <c r="I17" s="92">
-        <v>1</v>
-      </c>
-      <c r="J17" s="44">
+      <c r="F17" s="39">
+        <v>0</v>
+      </c>
+      <c r="G17" s="35">
+        <v>0</v>
+      </c>
+      <c r="H17" s="72">
+        <v>1</v>
+      </c>
+      <c r="I17" s="73">
+        <v>1</v>
+      </c>
+      <c r="J17" s="42">
         <v>0</v>
       </c>
       <c r="K17" s="12">
         <v>0</v>
       </c>
-      <c r="L17" s="45">
-        <v>0</v>
-      </c>
-      <c r="M17" s="13">
-        <v>0</v>
-      </c>
-      <c r="N17" s="46">
-        <v>0</v>
-      </c>
-      <c r="O17" s="14">
-        <v>0</v>
-      </c>
-      <c r="P17" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="15">
-        <v>0</v>
-      </c>
-      <c r="R17" s="17">
+      <c r="L17" s="43">
+        <v>0</v>
+      </c>
+      <c r="M17" s="86">
+        <v>0</v>
+      </c>
+      <c r="N17" s="44">
+        <v>0</v>
+      </c>
+      <c r="O17" s="13">
+        <v>0</v>
+      </c>
+      <c r="P17" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="14">
+        <v>0</v>
+      </c>
+      <c r="R17" s="16">
         <v>16</v>
       </c>
     </row>
@@ -2231,43 +2233,43 @@
       <c r="E18" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="41">
-        <v>0</v>
-      </c>
-      <c r="G18" s="37">
-        <v>0</v>
-      </c>
-      <c r="H18" s="91">
-        <v>1</v>
-      </c>
-      <c r="I18" s="92">
-        <v>1</v>
-      </c>
-      <c r="J18" s="44">
+      <c r="F18" s="39">
+        <v>0</v>
+      </c>
+      <c r="G18" s="35">
+        <v>0</v>
+      </c>
+      <c r="H18" s="72">
+        <v>1</v>
+      </c>
+      <c r="I18" s="73">
+        <v>1</v>
+      </c>
+      <c r="J18" s="42">
         <v>1</v>
       </c>
       <c r="K18" s="12">
         <v>0</v>
       </c>
-      <c r="L18" s="45">
-        <v>0</v>
-      </c>
-      <c r="M18" s="13">
-        <v>0</v>
-      </c>
-      <c r="N18" s="46">
-        <v>0</v>
-      </c>
-      <c r="O18" s="14">
-        <v>1</v>
-      </c>
-      <c r="P18" s="47">
+      <c r="L18" s="43">
+        <v>0</v>
+      </c>
+      <c r="M18" s="86">
+        <v>0</v>
+      </c>
+      <c r="N18" s="44">
+        <v>0</v>
+      </c>
+      <c r="O18" s="13">
+        <v>1</v>
+      </c>
+      <c r="P18" s="45">
         <v>0</v>
       </c>
       <c r="Q18" s="10">
         <v>0</v>
       </c>
-      <c r="R18" s="17">
+      <c r="R18" s="16">
         <v>17</v>
       </c>
     </row>
@@ -2287,43 +2289,43 @@
       <c r="E19" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F19" s="41">
-        <v>0</v>
-      </c>
-      <c r="G19" s="37">
-        <v>0</v>
-      </c>
-      <c r="H19" s="99">
-        <v>1</v>
-      </c>
-      <c r="I19" s="93">
-        <v>1</v>
-      </c>
-      <c r="J19" s="89">
-        <v>1</v>
-      </c>
-      <c r="K19" s="63">
-        <v>1</v>
-      </c>
-      <c r="L19" s="66">
-        <v>1</v>
-      </c>
-      <c r="M19" s="67">
-        <v>1</v>
-      </c>
-      <c r="N19" s="46">
-        <v>0</v>
-      </c>
-      <c r="O19" s="14">
-        <v>0</v>
-      </c>
-      <c r="P19" s="47">
+      <c r="F19" s="39">
+        <v>0</v>
+      </c>
+      <c r="G19" s="35">
+        <v>0</v>
+      </c>
+      <c r="H19" s="80">
+        <v>1</v>
+      </c>
+      <c r="I19" s="100">
+        <v>1</v>
+      </c>
+      <c r="J19" s="55">
+        <v>1</v>
+      </c>
+      <c r="K19" s="102">
+        <v>1</v>
+      </c>
+      <c r="L19" s="43">
+        <v>0</v>
+      </c>
+      <c r="M19" s="86">
+        <v>0</v>
+      </c>
+      <c r="N19" s="44">
+        <v>0</v>
+      </c>
+      <c r="O19" s="13">
+        <v>0</v>
+      </c>
+      <c r="P19" s="45">
         <v>0</v>
       </c>
       <c r="Q19" s="10">
         <v>0</v>
       </c>
-      <c r="R19" s="17">
+      <c r="R19" s="16">
         <v>18</v>
       </c>
     </row>
@@ -2343,43 +2345,43 @@
       <c r="E20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F20" s="41">
-        <v>0</v>
-      </c>
-      <c r="G20" s="37">
-        <v>0</v>
-      </c>
-      <c r="H20" s="43">
-        <v>0</v>
-      </c>
-      <c r="I20" s="25">
-        <v>0</v>
-      </c>
-      <c r="J20" s="44">
-        <v>0</v>
-      </c>
-      <c r="K20" s="12">
-        <v>0</v>
-      </c>
-      <c r="L20" s="66">
-        <v>1</v>
-      </c>
-      <c r="M20" s="67">
-        <v>1</v>
-      </c>
-      <c r="N20" s="46">
-        <v>0</v>
-      </c>
-      <c r="O20" s="14">
-        <v>0</v>
-      </c>
-      <c r="P20" s="47">
+      <c r="F20" s="39">
+        <v>0</v>
+      </c>
+      <c r="G20" s="35">
+        <v>0</v>
+      </c>
+      <c r="H20" s="41">
+        <v>0</v>
+      </c>
+      <c r="I20" s="23">
+        <v>0</v>
+      </c>
+      <c r="J20" s="54">
+        <v>0</v>
+      </c>
+      <c r="K20" s="94">
+        <v>0</v>
+      </c>
+      <c r="L20" s="101">
+        <v>1</v>
+      </c>
+      <c r="M20" s="99">
+        <v>1</v>
+      </c>
+      <c r="N20" s="44">
+        <v>0</v>
+      </c>
+      <c r="O20" s="13">
+        <v>0</v>
+      </c>
+      <c r="P20" s="45">
         <v>0</v>
       </c>
       <c r="Q20" s="10">
         <v>0</v>
       </c>
-      <c r="R20" s="17">
+      <c r="R20" s="16">
         <v>19</v>
       </c>
     </row>
@@ -2399,43 +2401,43 @@
       <c r="E21" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F21" s="41">
-        <v>0</v>
-      </c>
-      <c r="G21" s="37">
-        <v>0</v>
-      </c>
-      <c r="H21" s="94">
-        <v>1</v>
-      </c>
-      <c r="I21" s="95">
-        <v>1</v>
-      </c>
-      <c r="J21" s="54">
-        <v>1</v>
-      </c>
-      <c r="K21" s="70">
-        <v>1</v>
-      </c>
-      <c r="L21" s="68">
-        <v>1</v>
-      </c>
-      <c r="M21" s="69">
-        <v>1</v>
-      </c>
-      <c r="N21" s="46">
-        <v>0</v>
-      </c>
-      <c r="O21" s="14">
-        <v>0</v>
-      </c>
-      <c r="P21" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="15">
-        <v>0</v>
-      </c>
-      <c r="R21" s="17">
+      <c r="F21" s="39">
+        <v>0</v>
+      </c>
+      <c r="G21" s="35">
+        <v>0</v>
+      </c>
+      <c r="H21" s="75">
+        <v>1</v>
+      </c>
+      <c r="I21" s="76">
+        <v>1</v>
+      </c>
+      <c r="J21" s="52">
+        <v>1</v>
+      </c>
+      <c r="K21" s="56">
+        <v>1</v>
+      </c>
+      <c r="L21" s="43">
+        <v>0</v>
+      </c>
+      <c r="M21" s="86">
+        <v>0</v>
+      </c>
+      <c r="N21" s="44">
+        <v>0</v>
+      </c>
+      <c r="O21" s="13">
+        <v>0</v>
+      </c>
+      <c r="P21" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="14">
+        <v>0</v>
+      </c>
+      <c r="R21" s="16">
         <v>20</v>
       </c>
     </row>
@@ -2455,43 +2457,43 @@
       <c r="E22" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F22" s="41">
-        <v>0</v>
-      </c>
-      <c r="G22" s="37">
-        <v>0</v>
-      </c>
-      <c r="H22" s="43">
-        <v>0</v>
-      </c>
-      <c r="I22" s="25">
-        <v>0</v>
-      </c>
-      <c r="J22" s="56">
-        <v>1</v>
-      </c>
-      <c r="K22" s="61">
-        <v>1</v>
-      </c>
-      <c r="L22" s="45">
-        <v>0</v>
-      </c>
-      <c r="M22" s="13">
-        <v>0</v>
-      </c>
-      <c r="N22" s="46">
-        <v>0</v>
-      </c>
-      <c r="O22" s="14">
-        <v>0</v>
-      </c>
-      <c r="P22" s="47">
+      <c r="F22" s="39">
+        <v>0</v>
+      </c>
+      <c r="G22" s="35">
+        <v>0</v>
+      </c>
+      <c r="H22" s="41">
+        <v>0</v>
+      </c>
+      <c r="I22" s="23">
+        <v>0</v>
+      </c>
+      <c r="J22" s="53">
+        <v>1</v>
+      </c>
+      <c r="K22" s="12">
+        <v>1</v>
+      </c>
+      <c r="L22" s="43">
+        <v>0</v>
+      </c>
+      <c r="M22" s="86">
+        <v>0</v>
+      </c>
+      <c r="N22" s="44">
+        <v>0</v>
+      </c>
+      <c r="O22" s="13">
+        <v>0</v>
+      </c>
+      <c r="P22" s="45">
         <v>0</v>
       </c>
       <c r="Q22" s="10">
         <v>0</v>
       </c>
-      <c r="R22" s="17">
+      <c r="R22" s="16">
         <v>21</v>
       </c>
     </row>
@@ -2511,43 +2513,43 @@
       <c r="E23" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F23" s="41">
-        <v>0</v>
-      </c>
-      <c r="G23" s="37">
-        <v>0</v>
-      </c>
-      <c r="H23" s="83">
-        <v>1</v>
-      </c>
-      <c r="I23" s="90">
-        <v>1</v>
-      </c>
-      <c r="J23" s="56">
-        <v>1</v>
-      </c>
-      <c r="K23" s="61">
-        <v>1</v>
-      </c>
-      <c r="L23" s="64">
-        <v>1</v>
-      </c>
-      <c r="M23" s="65">
-        <v>1</v>
-      </c>
-      <c r="N23" s="46">
-        <v>0</v>
-      </c>
-      <c r="O23" s="14">
-        <v>0</v>
-      </c>
-      <c r="P23" s="47">
+      <c r="F23" s="39">
+        <v>0</v>
+      </c>
+      <c r="G23" s="35">
+        <v>0</v>
+      </c>
+      <c r="H23" s="65">
+        <v>1</v>
+      </c>
+      <c r="I23" s="71">
+        <v>1</v>
+      </c>
+      <c r="J23" s="53">
+        <v>1</v>
+      </c>
+      <c r="K23" s="12">
+        <v>1</v>
+      </c>
+      <c r="L23" s="43">
+        <v>0</v>
+      </c>
+      <c r="M23" s="86">
+        <v>0</v>
+      </c>
+      <c r="N23" s="44">
+        <v>0</v>
+      </c>
+      <c r="O23" s="13">
+        <v>0</v>
+      </c>
+      <c r="P23" s="45">
         <v>0</v>
       </c>
       <c r="Q23" s="10">
         <v>0</v>
       </c>
-      <c r="R23" s="17">
+      <c r="R23" s="16">
         <v>22</v>
       </c>
     </row>
@@ -2567,43 +2569,43 @@
       <c r="E24" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F24" s="41">
-        <v>0</v>
-      </c>
-      <c r="G24" s="37">
-        <v>0</v>
-      </c>
-      <c r="H24" s="91">
-        <v>1</v>
-      </c>
-      <c r="I24" s="92">
-        <v>1</v>
-      </c>
-      <c r="J24" s="56">
-        <v>1</v>
-      </c>
-      <c r="K24" s="61">
-        <v>1</v>
-      </c>
-      <c r="L24" s="45">
-        <v>0</v>
-      </c>
-      <c r="M24" s="13">
-        <v>0</v>
-      </c>
-      <c r="N24" s="46">
-        <v>0</v>
-      </c>
-      <c r="O24" s="14">
-        <v>0</v>
-      </c>
-      <c r="P24" s="47">
+      <c r="F24" s="39">
+        <v>0</v>
+      </c>
+      <c r="G24" s="35">
+        <v>0</v>
+      </c>
+      <c r="H24" s="72">
+        <v>1</v>
+      </c>
+      <c r="I24" s="73">
+        <v>1</v>
+      </c>
+      <c r="J24" s="53">
+        <v>1</v>
+      </c>
+      <c r="K24" s="12">
+        <v>1</v>
+      </c>
+      <c r="L24" s="43">
+        <v>0</v>
+      </c>
+      <c r="M24" s="86">
+        <v>0</v>
+      </c>
+      <c r="N24" s="44">
+        <v>0</v>
+      </c>
+      <c r="O24" s="13">
+        <v>0</v>
+      </c>
+      <c r="P24" s="45">
         <v>0</v>
       </c>
       <c r="Q24" s="10">
         <v>0</v>
       </c>
-      <c r="R24" s="17">
+      <c r="R24" s="16">
         <v>23</v>
       </c>
     </row>
@@ -2623,43 +2625,43 @@
       <c r="E25" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F25" s="41">
-        <v>0</v>
-      </c>
-      <c r="G25" s="37">
-        <v>0</v>
-      </c>
-      <c r="H25" s="85">
-        <v>1</v>
-      </c>
-      <c r="I25" s="93">
-        <v>1</v>
-      </c>
-      <c r="J25" s="58">
-        <v>1</v>
-      </c>
-      <c r="K25" s="59">
-        <v>1</v>
-      </c>
-      <c r="L25" s="45">
-        <v>0</v>
-      </c>
-      <c r="M25" s="13">
-        <v>0</v>
-      </c>
-      <c r="N25" s="46">
-        <v>0</v>
-      </c>
-      <c r="O25" s="14">
-        <v>0</v>
-      </c>
-      <c r="P25" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="15">
-        <v>0</v>
-      </c>
-      <c r="R25" s="17">
+      <c r="F25" s="39">
+        <v>0</v>
+      </c>
+      <c r="G25" s="35">
+        <v>0</v>
+      </c>
+      <c r="H25" s="67">
+        <v>1</v>
+      </c>
+      <c r="I25" s="74">
+        <v>1</v>
+      </c>
+      <c r="J25" s="54">
+        <v>1</v>
+      </c>
+      <c r="K25" s="82">
+        <v>1</v>
+      </c>
+      <c r="L25" s="43">
+        <v>0</v>
+      </c>
+      <c r="M25" s="86">
+        <v>0</v>
+      </c>
+      <c r="N25" s="44">
+        <v>0</v>
+      </c>
+      <c r="O25" s="13">
+        <v>0</v>
+      </c>
+      <c r="P25" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="14">
+        <v>0</v>
+      </c>
+      <c r="R25" s="16">
         <v>24</v>
       </c>
     </row>
@@ -2679,43 +2681,43 @@
       <c r="E26" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F26" s="41">
-        <v>0</v>
-      </c>
-      <c r="G26" s="37">
-        <v>0</v>
-      </c>
-      <c r="H26" s="43">
-        <v>1</v>
-      </c>
-      <c r="I26" s="25">
-        <v>0</v>
-      </c>
-      <c r="J26" s="44">
+      <c r="F26" s="39">
+        <v>0</v>
+      </c>
+      <c r="G26" s="35">
+        <v>0</v>
+      </c>
+      <c r="H26" s="41">
+        <v>1</v>
+      </c>
+      <c r="I26" s="23">
+        <v>0</v>
+      </c>
+      <c r="J26" s="42">
         <v>0</v>
       </c>
       <c r="K26" s="12">
         <v>0</v>
       </c>
-      <c r="L26" s="45">
-        <v>0</v>
-      </c>
-      <c r="M26" s="13">
-        <v>0</v>
-      </c>
-      <c r="N26" s="46">
-        <v>0</v>
-      </c>
-      <c r="O26" s="14">
-        <v>1</v>
-      </c>
-      <c r="P26" s="47">
+      <c r="L26" s="43">
+        <v>0</v>
+      </c>
+      <c r="M26" s="86">
+        <v>0</v>
+      </c>
+      <c r="N26" s="44">
+        <v>0</v>
+      </c>
+      <c r="O26" s="13">
+        <v>1</v>
+      </c>
+      <c r="P26" s="45">
         <v>0</v>
       </c>
       <c r="Q26" s="10">
         <v>0</v>
       </c>
-      <c r="R26" s="17">
+      <c r="R26" s="16">
         <v>25</v>
       </c>
     </row>
@@ -2735,43 +2737,43 @@
       <c r="E27" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F27" s="41">
-        <v>0</v>
-      </c>
-      <c r="G27" s="37">
-        <v>0</v>
-      </c>
-      <c r="H27" s="83">
-        <v>1</v>
-      </c>
-      <c r="I27" s="90">
-        <v>1</v>
-      </c>
-      <c r="J27" s="54">
-        <v>1</v>
-      </c>
-      <c r="K27" s="60">
-        <v>1</v>
-      </c>
-      <c r="L27" s="66">
-        <v>1</v>
-      </c>
-      <c r="M27" s="67">
-        <v>1</v>
-      </c>
-      <c r="N27" s="46">
-        <v>0</v>
-      </c>
-      <c r="O27" s="14">
-        <v>0</v>
-      </c>
-      <c r="P27" s="47">
+      <c r="F27" s="39">
+        <v>0</v>
+      </c>
+      <c r="G27" s="35">
+        <v>0</v>
+      </c>
+      <c r="H27" s="65">
+        <v>1</v>
+      </c>
+      <c r="I27" s="71">
+        <v>1</v>
+      </c>
+      <c r="J27" s="52">
+        <v>1</v>
+      </c>
+      <c r="K27" s="56">
+        <v>1</v>
+      </c>
+      <c r="L27" s="43">
+        <v>0</v>
+      </c>
+      <c r="M27" s="86">
+        <v>0</v>
+      </c>
+      <c r="N27" s="44">
+        <v>0</v>
+      </c>
+      <c r="O27" s="13">
+        <v>0</v>
+      </c>
+      <c r="P27" s="45">
         <v>0</v>
       </c>
       <c r="Q27" s="10">
         <v>0</v>
       </c>
-      <c r="R27" s="17">
+      <c r="R27" s="16">
         <v>26</v>
       </c>
     </row>
@@ -2791,43 +2793,43 @@
       <c r="E28" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F28" s="41">
-        <v>0</v>
-      </c>
-      <c r="G28" s="37">
-        <v>0</v>
-      </c>
-      <c r="H28" s="91">
-        <v>1</v>
-      </c>
-      <c r="I28" s="92">
-        <v>1</v>
-      </c>
-      <c r="J28" s="56">
-        <v>1</v>
-      </c>
-      <c r="K28" s="61">
-        <v>1</v>
-      </c>
-      <c r="L28" s="71">
-        <v>1</v>
-      </c>
-      <c r="M28" s="72">
-        <v>1</v>
-      </c>
-      <c r="N28" s="46">
-        <v>0</v>
-      </c>
-      <c r="O28" s="14">
-        <v>0</v>
-      </c>
-      <c r="P28" s="47">
+      <c r="F28" s="39">
+        <v>0</v>
+      </c>
+      <c r="G28" s="35">
+        <v>0</v>
+      </c>
+      <c r="H28" s="72">
+        <v>1</v>
+      </c>
+      <c r="I28" s="73">
+        <v>1</v>
+      </c>
+      <c r="J28" s="53">
+        <v>1</v>
+      </c>
+      <c r="K28" s="12">
+        <v>1</v>
+      </c>
+      <c r="L28" s="43">
+        <v>0</v>
+      </c>
+      <c r="M28" s="86">
+        <v>0</v>
+      </c>
+      <c r="N28" s="44">
+        <v>0</v>
+      </c>
+      <c r="O28" s="13">
+        <v>0</v>
+      </c>
+      <c r="P28" s="45">
         <v>0</v>
       </c>
       <c r="Q28" s="10">
         <v>0</v>
       </c>
-      <c r="R28" s="17">
+      <c r="R28" s="16">
         <v>27</v>
       </c>
     </row>
@@ -2847,43 +2849,43 @@
       <c r="E29" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F29" s="41">
-        <v>0</v>
-      </c>
-      <c r="G29" s="37">
-        <v>0</v>
-      </c>
-      <c r="H29" s="91">
-        <v>1</v>
-      </c>
-      <c r="I29" s="92">
-        <v>1</v>
-      </c>
-      <c r="J29" s="56">
-        <v>1</v>
-      </c>
-      <c r="K29" s="61">
-        <v>1</v>
-      </c>
-      <c r="L29" s="68">
-        <v>1</v>
-      </c>
-      <c r="M29" s="69">
-        <v>1</v>
-      </c>
-      <c r="N29" s="46">
-        <v>0</v>
-      </c>
-      <c r="O29" s="14">
-        <v>0</v>
-      </c>
-      <c r="P29" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="15">
-        <v>0</v>
-      </c>
-      <c r="R29" s="17">
+      <c r="F29" s="39">
+        <v>0</v>
+      </c>
+      <c r="G29" s="35">
+        <v>0</v>
+      </c>
+      <c r="H29" s="72">
+        <v>1</v>
+      </c>
+      <c r="I29" s="73">
+        <v>1</v>
+      </c>
+      <c r="J29" s="53">
+        <v>1</v>
+      </c>
+      <c r="K29" s="12">
+        <v>1</v>
+      </c>
+      <c r="L29" s="43">
+        <v>0</v>
+      </c>
+      <c r="M29" s="86">
+        <v>0</v>
+      </c>
+      <c r="N29" s="44">
+        <v>0</v>
+      </c>
+      <c r="O29" s="13">
+        <v>0</v>
+      </c>
+      <c r="P29" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="14">
+        <v>0</v>
+      </c>
+      <c r="R29" s="16">
         <v>28</v>
       </c>
     </row>
@@ -2903,43 +2905,43 @@
       <c r="E30" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F30" s="41">
-        <v>0</v>
-      </c>
-      <c r="G30" s="37">
-        <v>0</v>
-      </c>
-      <c r="H30" s="91">
-        <v>1</v>
-      </c>
-      <c r="I30" s="92">
-        <v>1</v>
-      </c>
-      <c r="J30" s="56">
-        <v>1</v>
-      </c>
-      <c r="K30" s="61">
-        <v>1</v>
-      </c>
-      <c r="L30" s="45">
-        <v>0</v>
-      </c>
-      <c r="M30" s="13">
-        <v>1</v>
-      </c>
-      <c r="N30" s="46">
-        <v>0</v>
-      </c>
-      <c r="O30" s="14">
-        <v>0</v>
-      </c>
-      <c r="P30" s="47">
+      <c r="F30" s="39">
+        <v>0</v>
+      </c>
+      <c r="G30" s="35">
+        <v>0</v>
+      </c>
+      <c r="H30" s="72">
+        <v>1</v>
+      </c>
+      <c r="I30" s="73">
+        <v>1</v>
+      </c>
+      <c r="J30" s="53">
+        <v>1</v>
+      </c>
+      <c r="K30" s="12">
+        <v>1</v>
+      </c>
+      <c r="L30" s="97">
+        <v>1</v>
+      </c>
+      <c r="M30" s="99">
+        <v>1</v>
+      </c>
+      <c r="N30" s="44">
+        <v>0</v>
+      </c>
+      <c r="O30" s="13">
+        <v>0</v>
+      </c>
+      <c r="P30" s="45">
         <v>0</v>
       </c>
       <c r="Q30" s="10">
         <v>0</v>
       </c>
-      <c r="R30" s="17">
+      <c r="R30" s="16">
         <v>29</v>
       </c>
     </row>
@@ -2959,43 +2961,43 @@
       <c r="E31" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F31" s="41">
-        <v>0</v>
-      </c>
-      <c r="G31" s="37">
-        <v>0</v>
-      </c>
-      <c r="H31" s="85">
-        <v>1</v>
-      </c>
-      <c r="I31" s="93">
-        <v>1</v>
-      </c>
-      <c r="J31" s="56">
-        <v>1</v>
-      </c>
-      <c r="K31" s="61">
-        <v>1</v>
-      </c>
-      <c r="L31" s="45">
-        <v>0</v>
-      </c>
-      <c r="M31" s="13">
-        <v>1</v>
-      </c>
-      <c r="N31" s="46">
-        <v>0</v>
-      </c>
-      <c r="O31" s="14">
-        <v>0</v>
-      </c>
-      <c r="P31" s="47">
+      <c r="F31" s="39">
+        <v>0</v>
+      </c>
+      <c r="G31" s="35">
+        <v>0</v>
+      </c>
+      <c r="H31" s="67">
+        <v>1</v>
+      </c>
+      <c r="I31" s="74">
+        <v>1</v>
+      </c>
+      <c r="J31" s="53">
+        <v>1</v>
+      </c>
+      <c r="K31" s="12">
+        <v>1</v>
+      </c>
+      <c r="L31" s="43">
+        <v>0</v>
+      </c>
+      <c r="M31" s="86">
+        <v>0</v>
+      </c>
+      <c r="N31" s="44">
+        <v>0</v>
+      </c>
+      <c r="O31" s="13">
+        <v>0</v>
+      </c>
+      <c r="P31" s="45">
         <v>0</v>
       </c>
       <c r="Q31" s="10">
         <v>0</v>
       </c>
-      <c r="R31" s="17">
+      <c r="R31" s="16">
         <v>30</v>
       </c>
     </row>
@@ -3015,43 +3017,43 @@
       <c r="E32" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F32" s="41">
-        <v>0</v>
-      </c>
-      <c r="G32" s="37">
-        <v>0</v>
-      </c>
-      <c r="H32" s="43">
-        <v>0</v>
-      </c>
-      <c r="I32" s="25">
-        <v>0</v>
-      </c>
-      <c r="J32" s="58">
-        <v>1</v>
-      </c>
-      <c r="K32" s="59">
-        <v>1</v>
-      </c>
-      <c r="L32" s="45">
-        <v>0</v>
-      </c>
-      <c r="M32" s="13">
-        <v>0</v>
-      </c>
-      <c r="N32" s="46">
-        <v>0</v>
-      </c>
-      <c r="O32" s="14">
-        <v>1</v>
-      </c>
-      <c r="P32" s="47">
+      <c r="F32" s="39">
+        <v>0</v>
+      </c>
+      <c r="G32" s="35">
+        <v>0</v>
+      </c>
+      <c r="H32" s="41">
+        <v>0</v>
+      </c>
+      <c r="I32" s="23">
+        <v>0</v>
+      </c>
+      <c r="J32" s="54">
+        <v>1</v>
+      </c>
+      <c r="K32" s="82">
+        <v>1</v>
+      </c>
+      <c r="L32" s="43">
+        <v>0</v>
+      </c>
+      <c r="M32" s="86">
+        <v>0</v>
+      </c>
+      <c r="N32" s="44">
+        <v>0</v>
+      </c>
+      <c r="O32" s="13">
+        <v>1</v>
+      </c>
+      <c r="P32" s="45">
         <v>0</v>
       </c>
       <c r="Q32" s="10">
         <v>0</v>
       </c>
-      <c r="R32" s="17">
+      <c r="R32" s="16">
         <v>31</v>
       </c>
     </row>
@@ -3071,43 +3073,43 @@
       <c r="E33" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F33" s="41">
-        <v>0</v>
-      </c>
-      <c r="G33" s="37">
-        <v>0</v>
-      </c>
-      <c r="H33" s="94">
-        <v>1</v>
-      </c>
-      <c r="I33" s="95">
-        <v>1</v>
-      </c>
-      <c r="J33" s="44">
+      <c r="F33" s="39">
+        <v>0</v>
+      </c>
+      <c r="G33" s="35">
+        <v>0</v>
+      </c>
+      <c r="H33" s="75">
+        <v>1</v>
+      </c>
+      <c r="I33" s="76">
+        <v>1</v>
+      </c>
+      <c r="J33" s="42">
         <v>0</v>
       </c>
       <c r="K33" s="12">
         <v>0</v>
       </c>
-      <c r="L33" s="45">
-        <v>0</v>
-      </c>
-      <c r="M33" s="13">
-        <v>0</v>
-      </c>
-      <c r="N33" s="73">
-        <v>1</v>
-      </c>
-      <c r="O33" s="75">
-        <v>1</v>
-      </c>
-      <c r="P33" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="15">
-        <v>0</v>
-      </c>
-      <c r="R33" s="17">
+      <c r="L33" s="43">
+        <v>0</v>
+      </c>
+      <c r="M33" s="86">
+        <v>0</v>
+      </c>
+      <c r="N33" s="83">
+        <v>1</v>
+      </c>
+      <c r="O33" s="59">
+        <v>1</v>
+      </c>
+      <c r="P33" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="14">
+        <v>0</v>
+      </c>
+      <c r="R33" s="16">
         <v>32</v>
       </c>
     </row>
@@ -3127,43 +3129,43 @@
       <c r="E34" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F34" s="41">
-        <v>0</v>
-      </c>
-      <c r="G34" s="38">
-        <v>0</v>
-      </c>
-      <c r="H34" s="43">
-        <v>1</v>
-      </c>
-      <c r="I34" s="26">
-        <v>0</v>
-      </c>
-      <c r="J34" s="44">
-        <v>0</v>
-      </c>
-      <c r="K34" s="18">
-        <v>0</v>
-      </c>
-      <c r="L34" s="45">
-        <v>0</v>
-      </c>
-      <c r="M34" s="19">
-        <v>0</v>
-      </c>
-      <c r="N34" s="46">
-        <v>1</v>
-      </c>
-      <c r="O34" s="20">
-        <v>0</v>
-      </c>
-      <c r="P34" s="80">
-        <v>1</v>
-      </c>
-      <c r="Q34" s="81">
-        <v>1</v>
-      </c>
-      <c r="R34" s="21">
+      <c r="F34" s="39">
+        <v>0</v>
+      </c>
+      <c r="G34" s="36">
+        <v>0</v>
+      </c>
+      <c r="H34" s="41">
+        <v>1</v>
+      </c>
+      <c r="I34" s="24">
+        <v>0</v>
+      </c>
+      <c r="J34" s="42">
+        <v>0</v>
+      </c>
+      <c r="K34" s="17">
+        <v>0</v>
+      </c>
+      <c r="L34" s="43">
+        <v>0</v>
+      </c>
+      <c r="M34" s="87">
+        <v>0</v>
+      </c>
+      <c r="N34" s="44">
+        <v>1</v>
+      </c>
+      <c r="O34" s="18">
+        <v>0</v>
+      </c>
+      <c r="P34" s="62">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="63">
+        <v>1</v>
+      </c>
+      <c r="R34" s="19">
         <v>33</v>
       </c>
     </row>
@@ -3183,43 +3185,43 @@
       <c r="E35" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F35" s="41">
-        <v>0</v>
-      </c>
-      <c r="G35" s="37">
-        <v>1</v>
-      </c>
-      <c r="H35" s="94">
-        <v>1</v>
-      </c>
-      <c r="I35" s="95">
-        <v>1</v>
-      </c>
-      <c r="J35" s="44">
+      <c r="F35" s="39">
+        <v>0</v>
+      </c>
+      <c r="G35" s="35">
+        <v>1</v>
+      </c>
+      <c r="H35" s="75">
+        <v>1</v>
+      </c>
+      <c r="I35" s="76">
+        <v>1</v>
+      </c>
+      <c r="J35" s="42">
         <v>0</v>
       </c>
       <c r="K35" s="12">
         <v>0</v>
       </c>
-      <c r="L35" s="45">
-        <v>0</v>
-      </c>
-      <c r="M35" s="13">
-        <v>0</v>
-      </c>
-      <c r="N35" s="76">
-        <v>1</v>
-      </c>
-      <c r="O35" s="77">
-        <v>1</v>
-      </c>
-      <c r="P35" s="47">
+      <c r="L35" s="43">
+        <v>0</v>
+      </c>
+      <c r="M35" s="86">
+        <v>0</v>
+      </c>
+      <c r="N35" s="84">
+        <v>1</v>
+      </c>
+      <c r="O35" s="60">
+        <v>1</v>
+      </c>
+      <c r="P35" s="45">
         <v>0</v>
       </c>
       <c r="Q35" s="10">
         <v>0</v>
       </c>
-      <c r="R35" s="17">
+      <c r="R35" s="16">
         <v>34</v>
       </c>
     </row>
@@ -3239,43 +3241,43 @@
       <c r="E36" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F36" s="41">
-        <v>0</v>
-      </c>
-      <c r="G36" s="37">
-        <v>0</v>
-      </c>
-      <c r="H36" s="43">
-        <v>1</v>
-      </c>
-      <c r="I36" s="25">
-        <v>0</v>
-      </c>
-      <c r="J36" s="44">
+      <c r="F36" s="39">
+        <v>0</v>
+      </c>
+      <c r="G36" s="35">
+        <v>0</v>
+      </c>
+      <c r="H36" s="41">
+        <v>1</v>
+      </c>
+      <c r="I36" s="23">
+        <v>0</v>
+      </c>
+      <c r="J36" s="42">
         <v>0</v>
       </c>
       <c r="K36" s="12">
         <v>0</v>
       </c>
-      <c r="L36" s="45">
-        <v>0</v>
-      </c>
-      <c r="M36" s="13">
-        <v>0</v>
-      </c>
-      <c r="N36" s="78">
-        <v>1</v>
-      </c>
-      <c r="O36" s="79">
-        <v>1</v>
-      </c>
-      <c r="P36" s="47">
+      <c r="L36" s="43">
+        <v>0</v>
+      </c>
+      <c r="M36" s="86">
+        <v>0</v>
+      </c>
+      <c r="N36" s="85">
+        <v>1</v>
+      </c>
+      <c r="O36" s="61">
+        <v>1</v>
+      </c>
+      <c r="P36" s="45">
         <v>0</v>
       </c>
       <c r="Q36" s="10">
         <v>0</v>
       </c>
-      <c r="R36" s="17">
+      <c r="R36" s="16">
         <v>35</v>
       </c>
     </row>
@@ -3295,43 +3297,43 @@
       <c r="E37" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F37" s="41">
-        <v>0</v>
-      </c>
-      <c r="G37" s="37">
-        <v>1</v>
-      </c>
-      <c r="H37" s="100">
-        <v>1</v>
-      </c>
-      <c r="I37" s="90">
-        <v>1</v>
-      </c>
-      <c r="J37" s="88">
-        <v>1</v>
-      </c>
-      <c r="K37" s="60">
-        <v>1</v>
-      </c>
-      <c r="L37" s="45">
-        <v>0</v>
-      </c>
-      <c r="M37" s="13">
-        <v>0</v>
-      </c>
-      <c r="N37" s="46">
-        <v>1</v>
-      </c>
-      <c r="O37" s="14">
-        <v>0</v>
-      </c>
-      <c r="P37" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="15">
-        <v>0</v>
-      </c>
-      <c r="R37" s="17">
+      <c r="F37" s="39">
+        <v>0</v>
+      </c>
+      <c r="G37" s="35">
+        <v>1</v>
+      </c>
+      <c r="H37" s="81">
+        <v>1</v>
+      </c>
+      <c r="I37" s="71">
+        <v>1</v>
+      </c>
+      <c r="J37" s="52">
+        <v>1</v>
+      </c>
+      <c r="K37" s="95">
+        <v>1</v>
+      </c>
+      <c r="L37" s="43">
+        <v>0</v>
+      </c>
+      <c r="M37" s="86">
+        <v>0</v>
+      </c>
+      <c r="N37" s="44">
+        <v>1</v>
+      </c>
+      <c r="O37" s="13">
+        <v>0</v>
+      </c>
+      <c r="P37" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="14">
+        <v>0</v>
+      </c>
+      <c r="R37" s="16">
         <v>36</v>
       </c>
     </row>
@@ -3351,43 +3353,43 @@
       <c r="E38" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F38" s="41">
-        <v>0</v>
-      </c>
-      <c r="G38" s="37">
-        <v>0</v>
-      </c>
-      <c r="H38" s="91">
-        <v>1</v>
-      </c>
-      <c r="I38" s="92">
-        <v>1</v>
-      </c>
-      <c r="J38" s="87">
-        <v>1</v>
-      </c>
-      <c r="K38" s="59">
-        <v>1</v>
-      </c>
-      <c r="L38" s="64">
-        <v>1</v>
-      </c>
-      <c r="M38" s="65">
-        <v>1</v>
-      </c>
-      <c r="N38" s="46">
-        <v>0</v>
-      </c>
-      <c r="O38" s="14">
-        <v>0</v>
-      </c>
-      <c r="P38" s="47">
+      <c r="F38" s="39">
+        <v>0</v>
+      </c>
+      <c r="G38" s="35">
+        <v>0</v>
+      </c>
+      <c r="H38" s="72">
+        <v>1</v>
+      </c>
+      <c r="I38" s="73">
+        <v>1</v>
+      </c>
+      <c r="J38" s="54">
+        <v>1</v>
+      </c>
+      <c r="K38" s="94">
+        <v>1</v>
+      </c>
+      <c r="L38" s="97">
+        <v>1</v>
+      </c>
+      <c r="M38" s="99">
+        <v>1</v>
+      </c>
+      <c r="N38" s="44">
+        <v>0</v>
+      </c>
+      <c r="O38" s="13">
+        <v>0</v>
+      </c>
+      <c r="P38" s="45">
         <v>0</v>
       </c>
       <c r="Q38" s="10">
         <v>0</v>
       </c>
-      <c r="R38" s="17">
+      <c r="R38" s="16">
         <v>37</v>
       </c>
     </row>
@@ -3407,43 +3409,43 @@
       <c r="E39" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F39" s="41">
-        <v>1</v>
-      </c>
-      <c r="G39" s="37">
-        <v>1</v>
-      </c>
-      <c r="H39" s="85">
-        <v>1</v>
-      </c>
-      <c r="I39" s="93">
-        <v>1</v>
-      </c>
-      <c r="J39" s="44">
+      <c r="F39" s="39">
+        <v>1</v>
+      </c>
+      <c r="G39" s="35">
+        <v>1</v>
+      </c>
+      <c r="H39" s="67">
+        <v>1</v>
+      </c>
+      <c r="I39" s="74">
+        <v>1</v>
+      </c>
+      <c r="J39" s="42">
         <v>0</v>
       </c>
       <c r="K39" s="12">
         <v>1</v>
       </c>
-      <c r="L39" s="45">
-        <v>0</v>
-      </c>
-      <c r="M39" s="13">
-        <v>0</v>
-      </c>
-      <c r="N39" s="76">
-        <v>1</v>
-      </c>
-      <c r="O39" s="77">
-        <v>1</v>
-      </c>
-      <c r="P39" s="47">
+      <c r="L39" s="43">
+        <v>0</v>
+      </c>
+      <c r="M39" s="86">
+        <v>0</v>
+      </c>
+      <c r="N39" s="84">
+        <v>1</v>
+      </c>
+      <c r="O39" s="60">
+        <v>1</v>
+      </c>
+      <c r="P39" s="45">
         <v>0</v>
       </c>
       <c r="Q39" s="10">
         <v>0</v>
       </c>
-      <c r="R39" s="17">
+      <c r="R39" s="16">
         <v>38</v>
       </c>
     </row>
@@ -3463,43 +3465,43 @@
       <c r="E40" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F40" s="41">
-        <v>1</v>
-      </c>
-      <c r="G40" s="37">
-        <v>1</v>
-      </c>
-      <c r="H40" s="43">
-        <v>1</v>
-      </c>
-      <c r="I40" s="25">
-        <v>0</v>
-      </c>
-      <c r="J40" s="44">
+      <c r="F40" s="39">
+        <v>1</v>
+      </c>
+      <c r="G40" s="35">
+        <v>1</v>
+      </c>
+      <c r="H40" s="41">
+        <v>1</v>
+      </c>
+      <c r="I40" s="23">
+        <v>0</v>
+      </c>
+      <c r="J40" s="42">
         <v>0</v>
       </c>
       <c r="K40" s="12">
         <v>0</v>
       </c>
-      <c r="L40" s="45">
-        <v>0</v>
-      </c>
-      <c r="M40" s="13">
-        <v>0</v>
-      </c>
-      <c r="N40" s="78">
-        <v>1</v>
-      </c>
-      <c r="O40" s="79">
-        <v>1</v>
-      </c>
-      <c r="P40" s="47">
+      <c r="L40" s="43">
+        <v>0</v>
+      </c>
+      <c r="M40" s="86">
+        <v>0</v>
+      </c>
+      <c r="N40" s="85">
+        <v>1</v>
+      </c>
+      <c r="O40" s="61">
+        <v>1</v>
+      </c>
+      <c r="P40" s="45">
         <v>0</v>
       </c>
       <c r="Q40" s="10">
         <v>0</v>
       </c>
-      <c r="R40" s="17">
+      <c r="R40" s="16">
         <v>39</v>
       </c>
     </row>
@@ -3519,43 +3521,43 @@
       <c r="E41" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F41" s="41">
-        <v>0</v>
-      </c>
-      <c r="G41" s="37">
-        <v>0</v>
-      </c>
-      <c r="H41" s="83">
-        <v>1</v>
-      </c>
-      <c r="I41" s="90">
-        <v>1</v>
-      </c>
-      <c r="J41" s="88">
-        <v>1</v>
-      </c>
-      <c r="K41" s="60">
-        <v>1</v>
-      </c>
-      <c r="L41" s="45">
-        <v>0</v>
-      </c>
-      <c r="M41" s="13">
-        <v>0</v>
-      </c>
-      <c r="N41" s="46">
-        <v>0</v>
-      </c>
-      <c r="O41" s="14">
-        <v>0</v>
-      </c>
-      <c r="P41" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="15">
-        <v>0</v>
-      </c>
-      <c r="R41" s="17">
+      <c r="F41" s="39">
+        <v>0</v>
+      </c>
+      <c r="G41" s="35">
+        <v>0</v>
+      </c>
+      <c r="H41" s="65">
+        <v>1</v>
+      </c>
+      <c r="I41" s="71">
+        <v>1</v>
+      </c>
+      <c r="J41" s="52">
+        <v>1</v>
+      </c>
+      <c r="K41" s="95">
+        <v>1</v>
+      </c>
+      <c r="L41" s="43">
+        <v>0</v>
+      </c>
+      <c r="M41" s="86">
+        <v>0</v>
+      </c>
+      <c r="N41" s="44">
+        <v>0</v>
+      </c>
+      <c r="O41" s="13">
+        <v>0</v>
+      </c>
+      <c r="P41" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="14">
+        <v>0</v>
+      </c>
+      <c r="R41" s="16">
         <v>40</v>
       </c>
     </row>
@@ -3575,43 +3577,43 @@
       <c r="E42" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F42" s="48">
-        <v>1</v>
-      </c>
-      <c r="G42" s="96">
-        <v>1</v>
-      </c>
-      <c r="H42" s="91">
-        <v>1</v>
-      </c>
-      <c r="I42" s="92">
-        <v>1</v>
-      </c>
-      <c r="J42" s="87">
-        <v>1</v>
-      </c>
-      <c r="K42" s="59">
-        <v>1</v>
-      </c>
-      <c r="L42" s="64">
-        <v>1</v>
-      </c>
-      <c r="M42" s="65">
-        <v>1</v>
-      </c>
-      <c r="N42" s="46">
-        <v>0</v>
-      </c>
-      <c r="O42" s="14">
-        <v>0</v>
-      </c>
-      <c r="P42" s="47">
+      <c r="F42" s="46">
+        <v>1</v>
+      </c>
+      <c r="G42" s="77">
+        <v>1</v>
+      </c>
+      <c r="H42" s="72">
+        <v>1</v>
+      </c>
+      <c r="I42" s="73">
+        <v>1</v>
+      </c>
+      <c r="J42" s="54">
+        <v>1</v>
+      </c>
+      <c r="K42" s="94">
+        <v>1</v>
+      </c>
+      <c r="L42" s="97">
+        <v>1</v>
+      </c>
+      <c r="M42" s="99">
+        <v>1</v>
+      </c>
+      <c r="N42" s="44">
+        <v>0</v>
+      </c>
+      <c r="O42" s="13">
+        <v>0</v>
+      </c>
+      <c r="P42" s="45">
         <v>0</v>
       </c>
       <c r="Q42" s="10">
         <v>0</v>
       </c>
-      <c r="R42" s="17">
+      <c r="R42" s="16">
         <v>41</v>
       </c>
     </row>
@@ -3631,43 +3633,43 @@
       <c r="E43" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F43" s="51">
-        <v>1</v>
-      </c>
-      <c r="G43" s="37">
-        <v>1</v>
-      </c>
-      <c r="H43" s="91">
-        <v>1</v>
-      </c>
-      <c r="I43" s="92">
-        <v>1</v>
-      </c>
-      <c r="J43" s="44">
+      <c r="F43" s="49">
+        <v>1</v>
+      </c>
+      <c r="G43" s="35">
+        <v>1</v>
+      </c>
+      <c r="H43" s="72">
+        <v>1</v>
+      </c>
+      <c r="I43" s="73">
+        <v>1</v>
+      </c>
+      <c r="J43" s="42">
         <v>1</v>
       </c>
       <c r="K43" s="12">
         <v>0</v>
       </c>
-      <c r="L43" s="45">
-        <v>0</v>
-      </c>
-      <c r="M43" s="13">
-        <v>0</v>
-      </c>
-      <c r="N43" s="46">
-        <v>0</v>
-      </c>
-      <c r="O43" s="14">
-        <v>1</v>
-      </c>
-      <c r="P43" s="47">
+      <c r="L43" s="43">
+        <v>0</v>
+      </c>
+      <c r="M43" s="86">
+        <v>0</v>
+      </c>
+      <c r="N43" s="44">
+        <v>0</v>
+      </c>
+      <c r="O43" s="13">
+        <v>1</v>
+      </c>
+      <c r="P43" s="45">
         <v>0</v>
       </c>
       <c r="Q43" s="10">
         <v>0</v>
       </c>
-      <c r="R43" s="17">
+      <c r="R43" s="16">
         <v>42</v>
       </c>
     </row>
@@ -3687,43 +3689,43 @@
       <c r="E44" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F44" s="51">
-        <v>1</v>
-      </c>
-      <c r="G44" s="37">
-        <v>1</v>
-      </c>
-      <c r="H44" s="85">
-        <v>1</v>
-      </c>
-      <c r="I44" s="93">
-        <v>1</v>
-      </c>
-      <c r="J44" s="89">
-        <v>1</v>
-      </c>
-      <c r="K44" s="63">
-        <v>1</v>
-      </c>
-      <c r="L44" s="45">
-        <v>0</v>
-      </c>
-      <c r="M44" s="13">
-        <v>1</v>
-      </c>
-      <c r="N44" s="46">
-        <v>0</v>
-      </c>
-      <c r="O44" s="14">
-        <v>0</v>
-      </c>
-      <c r="P44" s="47">
+      <c r="F44" s="49">
+        <v>1</v>
+      </c>
+      <c r="G44" s="35">
+        <v>1</v>
+      </c>
+      <c r="H44" s="67">
+        <v>1</v>
+      </c>
+      <c r="I44" s="74">
+        <v>1</v>
+      </c>
+      <c r="J44" s="55">
+        <v>1</v>
+      </c>
+      <c r="K44" s="102">
+        <v>1</v>
+      </c>
+      <c r="L44" s="43">
+        <v>0</v>
+      </c>
+      <c r="M44" s="86">
+        <v>0</v>
+      </c>
+      <c r="N44" s="44">
+        <v>0</v>
+      </c>
+      <c r="O44" s="13">
+        <v>0</v>
+      </c>
+      <c r="P44" s="45">
         <v>0</v>
       </c>
       <c r="Q44" s="10">
         <v>0</v>
       </c>
-      <c r="R44" s="17">
+      <c r="R44" s="16">
         <v>43</v>
       </c>
     </row>
@@ -3743,43 +3745,43 @@
       <c r="E45" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F45" s="50">
-        <v>1</v>
-      </c>
-      <c r="G45" s="52">
-        <v>1</v>
-      </c>
-      <c r="H45" s="43">
-        <v>0</v>
-      </c>
-      <c r="I45" s="25">
-        <v>0</v>
-      </c>
-      <c r="J45" s="44">
+      <c r="F45" s="48">
+        <v>1</v>
+      </c>
+      <c r="G45" s="50">
+        <v>1</v>
+      </c>
+      <c r="H45" s="41">
+        <v>0</v>
+      </c>
+      <c r="I45" s="23">
+        <v>0</v>
+      </c>
+      <c r="J45" s="42">
         <v>0</v>
       </c>
       <c r="K45" s="12">
         <v>0</v>
       </c>
-      <c r="L45" s="45">
-        <v>0</v>
-      </c>
-      <c r="M45" s="13">
-        <v>0</v>
-      </c>
-      <c r="N45" s="73">
-        <v>1</v>
-      </c>
-      <c r="O45" s="75">
-        <v>1</v>
-      </c>
-      <c r="P45" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="15">
-        <v>0</v>
-      </c>
-      <c r="R45" s="17">
+      <c r="L45" s="43">
+        <v>0</v>
+      </c>
+      <c r="M45" s="86">
+        <v>0</v>
+      </c>
+      <c r="N45" s="83">
+        <v>1</v>
+      </c>
+      <c r="O45" s="59">
+        <v>1</v>
+      </c>
+      <c r="P45" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="14">
+        <v>0</v>
+      </c>
+      <c r="R45" s="16">
         <v>44</v>
       </c>
     </row>
@@ -3799,43 +3801,43 @@
       <c r="E46" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F46" s="41">
-        <v>0</v>
-      </c>
-      <c r="G46" s="37">
-        <v>0</v>
-      </c>
-      <c r="H46" s="83">
-        <v>1</v>
-      </c>
-      <c r="I46" s="90">
-        <v>1</v>
-      </c>
-      <c r="J46" s="44">
+      <c r="F46" s="39">
+        <v>0</v>
+      </c>
+      <c r="G46" s="35">
+        <v>0</v>
+      </c>
+      <c r="H46" s="65">
+        <v>1</v>
+      </c>
+      <c r="I46" s="71">
+        <v>1</v>
+      </c>
+      <c r="J46" s="42">
         <v>0</v>
       </c>
       <c r="K46" s="12">
         <v>0</v>
       </c>
-      <c r="L46" s="45">
-        <v>0</v>
-      </c>
-      <c r="M46" s="13">
-        <v>0</v>
-      </c>
-      <c r="N46" s="46">
-        <v>0</v>
-      </c>
-      <c r="O46" s="14">
-        <v>0</v>
-      </c>
-      <c r="P46" s="47">
+      <c r="L46" s="43">
+        <v>0</v>
+      </c>
+      <c r="M46" s="86">
+        <v>0</v>
+      </c>
+      <c r="N46" s="44">
+        <v>0</v>
+      </c>
+      <c r="O46" s="13">
+        <v>0</v>
+      </c>
+      <c r="P46" s="45">
         <v>0</v>
       </c>
       <c r="Q46" s="10">
         <v>0</v>
       </c>
-      <c r="R46" s="17">
+      <c r="R46" s="16">
         <v>45</v>
       </c>
     </row>
@@ -3855,43 +3857,43 @@
       <c r="E47" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F47" s="53">
-        <v>1</v>
-      </c>
-      <c r="G47" s="97">
-        <v>1</v>
-      </c>
-      <c r="H47" s="91">
-        <v>1</v>
-      </c>
-      <c r="I47" s="92">
-        <v>1</v>
-      </c>
-      <c r="J47" s="89">
-        <v>1</v>
-      </c>
-      <c r="K47" s="63">
-        <v>1</v>
-      </c>
-      <c r="L47" s="45">
-        <v>0</v>
-      </c>
-      <c r="M47" s="13">
-        <v>0</v>
-      </c>
-      <c r="N47" s="46">
-        <v>0</v>
-      </c>
-      <c r="O47" s="14">
-        <v>0</v>
-      </c>
-      <c r="P47" s="47">
+      <c r="F47" s="51">
+        <v>1</v>
+      </c>
+      <c r="G47" s="78">
+        <v>1</v>
+      </c>
+      <c r="H47" s="72">
+        <v>1</v>
+      </c>
+      <c r="I47" s="73">
+        <v>1</v>
+      </c>
+      <c r="J47" s="55">
+        <v>1</v>
+      </c>
+      <c r="K47" s="102">
+        <v>1</v>
+      </c>
+      <c r="L47" s="43">
+        <v>0</v>
+      </c>
+      <c r="M47" s="86">
+        <v>0</v>
+      </c>
+      <c r="N47" s="44">
+        <v>0</v>
+      </c>
+      <c r="O47" s="13">
+        <v>0</v>
+      </c>
+      <c r="P47" s="45">
         <v>0</v>
       </c>
       <c r="Q47" s="10">
         <v>0</v>
       </c>
-      <c r="R47" s="17">
+      <c r="R47" s="16">
         <v>46</v>
       </c>
     </row>
@@ -3911,43 +3913,43 @@
       <c r="E48" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F48" s="41">
-        <v>0</v>
-      </c>
-      <c r="G48" s="37">
-        <v>0</v>
-      </c>
-      <c r="H48" s="91">
-        <v>1</v>
-      </c>
-      <c r="I48" s="92">
-        <v>1</v>
-      </c>
-      <c r="J48" s="44">
+      <c r="F48" s="39">
+        <v>0</v>
+      </c>
+      <c r="G48" s="35">
+        <v>0</v>
+      </c>
+      <c r="H48" s="72">
+        <v>1</v>
+      </c>
+      <c r="I48" s="73">
+        <v>1</v>
+      </c>
+      <c r="J48" s="42">
         <v>0</v>
       </c>
       <c r="K48" s="12">
         <v>0</v>
       </c>
-      <c r="L48" s="45">
-        <v>0</v>
-      </c>
-      <c r="M48" s="13">
-        <v>0</v>
-      </c>
-      <c r="N48" s="46">
-        <v>0</v>
-      </c>
-      <c r="O48" s="14">
-        <v>0</v>
-      </c>
-      <c r="P48" s="47">
+      <c r="L48" s="43">
+        <v>0</v>
+      </c>
+      <c r="M48" s="86">
+        <v>0</v>
+      </c>
+      <c r="N48" s="44">
+        <v>0</v>
+      </c>
+      <c r="O48" s="13">
+        <v>0</v>
+      </c>
+      <c r="P48" s="45">
         <v>1</v>
       </c>
       <c r="Q48" s="10">
         <v>0</v>
       </c>
-      <c r="R48" s="17">
+      <c r="R48" s="16">
         <v>47</v>
       </c>
     </row>
@@ -3967,43 +3969,43 @@
       <c r="E49" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F49" s="53">
-        <v>1</v>
-      </c>
-      <c r="G49" s="97">
-        <v>1</v>
-      </c>
-      <c r="H49" s="85">
-        <v>1</v>
-      </c>
-      <c r="I49" s="93">
-        <v>1</v>
-      </c>
-      <c r="J49" s="44">
+      <c r="F49" s="51">
+        <v>1</v>
+      </c>
+      <c r="G49" s="78">
+        <v>1</v>
+      </c>
+      <c r="H49" s="67">
+        <v>1</v>
+      </c>
+      <c r="I49" s="74">
+        <v>1</v>
+      </c>
+      <c r="J49" s="42">
         <v>0</v>
       </c>
       <c r="K49" s="12">
         <v>0</v>
       </c>
-      <c r="L49" s="45">
-        <v>0</v>
-      </c>
-      <c r="M49" s="13">
-        <v>0</v>
-      </c>
-      <c r="N49" s="73">
-        <v>1</v>
-      </c>
-      <c r="O49" s="75">
-        <v>1</v>
-      </c>
-      <c r="P49" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="15">
-        <v>0</v>
-      </c>
-      <c r="R49" s="17">
+      <c r="L49" s="43">
+        <v>0</v>
+      </c>
+      <c r="M49" s="86">
+        <v>0</v>
+      </c>
+      <c r="N49" s="83">
+        <v>1</v>
+      </c>
+      <c r="O49" s="59">
+        <v>1</v>
+      </c>
+      <c r="P49" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="14">
+        <v>0</v>
+      </c>
+      <c r="R49" s="16">
         <v>48</v>
       </c>
     </row>
@@ -4023,43 +4025,43 @@
       <c r="E50" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F50" s="41">
-        <v>0</v>
-      </c>
-      <c r="G50" s="37">
-        <v>0</v>
-      </c>
-      <c r="H50" s="43">
-        <v>0</v>
-      </c>
-      <c r="I50" s="25">
-        <v>1</v>
-      </c>
-      <c r="J50" s="62">
-        <v>1</v>
-      </c>
-      <c r="K50" s="63">
-        <v>1</v>
-      </c>
-      <c r="L50" s="45">
-        <v>0</v>
-      </c>
-      <c r="M50" s="13">
-        <v>0</v>
-      </c>
-      <c r="N50" s="46">
-        <v>0</v>
-      </c>
-      <c r="O50" s="14">
-        <v>0</v>
-      </c>
-      <c r="P50" s="47">
+      <c r="F50" s="39">
+        <v>0</v>
+      </c>
+      <c r="G50" s="35">
+        <v>0</v>
+      </c>
+      <c r="H50" s="41">
+        <v>0</v>
+      </c>
+      <c r="I50" s="23">
+        <v>1</v>
+      </c>
+      <c r="J50" s="55">
+        <v>1</v>
+      </c>
+      <c r="K50" s="102">
+        <v>1</v>
+      </c>
+      <c r="L50" s="43">
+        <v>0</v>
+      </c>
+      <c r="M50" s="86">
+        <v>0</v>
+      </c>
+      <c r="N50" s="44">
+        <v>0</v>
+      </c>
+      <c r="O50" s="13">
+        <v>0</v>
+      </c>
+      <c r="P50" s="45">
         <v>0</v>
       </c>
       <c r="Q50" s="10">
         <v>0</v>
       </c>
-      <c r="R50" s="17">
+      <c r="R50" s="16">
         <v>49</v>
       </c>
     </row>
@@ -4079,64 +4081,64 @@
       <c r="E51" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F51" s="41">
-        <v>0</v>
-      </c>
-      <c r="G51" s="37">
-        <v>0</v>
-      </c>
-      <c r="H51" s="94">
-        <v>1</v>
-      </c>
-      <c r="I51" s="95">
-        <v>1</v>
-      </c>
-      <c r="J51" s="44">
+      <c r="F51" s="39">
+        <v>0</v>
+      </c>
+      <c r="G51" s="35">
+        <v>0</v>
+      </c>
+      <c r="H51" s="75">
+        <v>1</v>
+      </c>
+      <c r="I51" s="76">
+        <v>1</v>
+      </c>
+      <c r="J51" s="42">
         <v>0</v>
       </c>
       <c r="K51" s="12">
         <v>0</v>
       </c>
-      <c r="L51" s="64">
-        <v>1</v>
-      </c>
-      <c r="M51" s="65">
-        <v>1</v>
-      </c>
-      <c r="N51" s="46">
-        <v>0</v>
-      </c>
-      <c r="O51" s="14">
-        <v>0</v>
-      </c>
-      <c r="P51" s="47">
+      <c r="L51" s="43">
+        <v>0</v>
+      </c>
+      <c r="M51" s="86">
+        <v>0</v>
+      </c>
+      <c r="N51" s="44">
+        <v>0</v>
+      </c>
+      <c r="O51" s="13">
+        <v>0</v>
+      </c>
+      <c r="P51" s="45">
         <v>0</v>
       </c>
       <c r="Q51" s="10">
         <v>0</v>
       </c>
-      <c r="R51" s="17">
+      <c r="R51" s="16">
         <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F52" s="42">
+      <c r="F52" s="40">
         <f t="shared" ref="F52:P52" si="0">SUM(F2:F51)</f>
         <v>11</v>
       </c>
-      <c r="G52" s="39">
+      <c r="G52" s="37">
         <f t="shared" ref="G52" si="1">SUM(G2:G51)</f>
         <v>14</v>
       </c>
-      <c r="H52" s="42">
+      <c r="H52" s="40">
         <f>SUM(H2:H51)</f>
         <v>41</v>
       </c>
-      <c r="I52" s="27">
+      <c r="I52" s="25">
         <f t="shared" ref="I52" si="2">SUM(I2:I51)</f>
         <v>38</v>
       </c>
-      <c r="J52" s="42">
+      <c r="J52" s="40">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
@@ -4144,15 +4146,15 @@
         <f t="shared" ref="K52" si="3">SUM(K2:K51)</f>
         <v>31</v>
       </c>
-      <c r="L52" s="42">
+      <c r="L52" s="40">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="M52" s="1">
         <f t="shared" ref="M52" si="4">SUM(M2:M51)</f>
-        <v>18</v>
-      </c>
-      <c r="N52" s="42">
+        <v>7</v>
+      </c>
+      <c r="N52" s="40">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -4160,7 +4162,7 @@
         <f t="shared" ref="O52" si="5">SUM(O2:O51)</f>
         <v>15</v>
       </c>
-      <c r="P52" s="42">
+      <c r="P52" s="40">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -4168,7 +4170,7 @@
         <f t="shared" ref="Q52" si="6">SUM(Q2:Q51)</f>
         <v>1</v>
       </c>
-      <c r="R52" s="22"/>
+      <c r="R52" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
